--- a/artfynd/A 28738-2026 artfynd.xlsx
+++ b/artfynd/A 28738-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135437116</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135436936</v>
       </c>
       <c r="B4" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>135437002</v>
       </c>
       <c r="B5" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>135437083</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>135437270</v>
       </c>
       <c r="B7" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>135437323</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1407,7 +1407,7 @@
         <v>135436985</v>
       </c>
       <c r="B9" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,7 +1514,7 @@
         <v>135437214</v>
       </c>
       <c r="B10" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>135437032</v>
       </c>
       <c r="B12" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         <v>135437128</v>
       </c>
       <c r="B13" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
